--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1591-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1591-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CF0EEBF-E6DD-4359-A530-D2F3F7160221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E61C238C-684B-4A12-B1CE-2BED02B49C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{21C37953-C77A-479F-951D-EBFD05775807}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{8C4D8D58-13E0-415D-9186-D573803BC8CE}"/>
   </bookViews>
   <sheets>
     <sheet name="1591-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1541,25 +1541,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF38B3B-F146-454C-A4A3-BA746A0D553B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CD49FB-2035-4A0E-90DB-16EC39556FD2}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1749,7 +1749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>2024</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2023</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="42">
         <v>2022</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="44">
         <v>2021</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="46"/>
       <c r="B20" s="47"/>
       <c r="C20" s="20" t="s">
@@ -2877,7 +2877,7 @@
       <c r="W20" s="53"/>
       <c r="X20" s="49"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="50" t="s">
         <v>29</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="51"/>
       <c r="B22" s="51"/>
       <c r="C22" s="22" t="s">
@@ -2979,7 +2979,7 @@
       <c r="W22" s="53"/>
       <c r="X22" s="49"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2020</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2019</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="42">
         <v>2018</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>2017</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="42">
         <v>2016</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>2015</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>2014</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>2013</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>2012</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>2011</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>2010</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>2009</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="42" t="s">
         <v>51</v>
       </c>
